--- a/site/ADP-Workforce-Now-SQL-Server-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-SQL-Server-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Examples for Creating a View in Microsoft SQL Server</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,44 +793,154 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>View: V_Worker</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KJCJVNSSBAHYMBQZ0MXM3VV6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SQL-Server-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SQL-Server-Integration-Guide/#h_01KJCJVNSSBAHYMBQZ0MXM3VV6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>View: V_Worker_Assignments</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KJCJXG42SG29YYN50ZTKHV1P</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SQL-Server-Integration-Guide/#h_01KJCJXG42SG29YYN50ZTKHV1P</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>View: V_Payroll_Summary</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KJCK0CV8VPN7W9NEV50M7YV0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SQL-Server-Integration-Guide/#h_01KJCK0CV8VPN7W9NEV50M7YV0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KJCK47F7K0E2S5DKA8201FZN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SQL-Server-Integration-Guide/#h_01KJCK47F7K0E2S5DKA8201FZN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SQL-Server-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SQL-Server-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Entity Relationship Diagrams</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KJCCVHRE488AV2FHQJBF1P7G</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SQL-Server-Integration-Guide/#h_01KJCCVHRE488AV2FHQJBF1P7G</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Workforce-Now-SQL-Server-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-SQL-Server-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,6 +944,28 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Troubleshooting</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KK1QZYWNFS5NHNPFR2DE6V61</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SQL-Server-Integration-Guide/#h_01KK1QZYWNFS5NHNPFR2DE6V61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
